--- a/tame_output/ON/bt/strategyON_20240305.xlsx
+++ b/tame_output/ON/bt/strategyON_20240305.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-284.3%</t>
+          <t>-323.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,32 +992,32 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
+          <t>13.4%</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-17.6%</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>12.4%</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-16.0%</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>-0.2</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>13.8%</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.5%</t>
+          <t>299.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-97.3%</t>
+          <t>-91.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-89.5%</t>
+          <t>-93.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>82.9%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-114.1%</t>
+          <t>-129.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-28.9%</t>
+          <t>-30.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-1.238542144722925</v>
+        <v>-1.631089855992144</v>
       </c>
       <c r="E1858" t="n">
-        <v>2.641965364360462</v>
+        <v>2.484946279852775</v>
       </c>
       <c r="F1858" t="n">
         <v>0.4893371670236317</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-1.240692664503136</v>
+        <v>-1.633240375772355</v>
       </c>
       <c r="E1859" t="n">
-        <v>2.627438043915782</v>
+        <v>2.470418959408094</v>
       </c>
       <c r="F1859" t="n">
         <v>0.4876891591850335</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-1.227630410154168</v>
+        <v>-1.620178121423388</v>
       </c>
       <c r="E1860" t="n">
-        <v>2.62094772065746</v>
+        <v>2.463928636149772</v>
       </c>
       <c r="F1860" t="n">
         <v>0.4935237059751</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-1.229194561264471</v>
+        <v>-1.621742272533691</v>
       </c>
       <c r="E1861" t="n">
-        <v>2.618902651869304</v>
+        <v>2.461883567361616</v>
       </c>
       <c r="F1861" t="n">
         <v>0.4935237059751</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309427</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-1.227145976402761</v>
+        <v>-1.61969368767198</v>
       </c>
       <c r="E1862" t="n">
-        <v>2.62620964604823</v>
+        <v>2.469190561540542</v>
       </c>
       <c r="F1862" t="n">
         <v>0.4957714060332924</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970908</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-1.224718911874042</v>
+        <v>-1.617266623143262</v>
       </c>
       <c r="E1863" t="n">
-        <v>2.626434986865549</v>
+        <v>2.469415902357861</v>
       </c>
       <c r="F1863" t="n">
         <v>0.4954386242261408</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-1.22601093364838</v>
+        <v>-1.6185586449176</v>
       </c>
       <c r="E1864" t="n">
-        <v>2.624679722170572</v>
+        <v>2.467660637662885</v>
       </c>
       <c r="F1864" t="n">
         <v>0.4941466024518028</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191741</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-1.230825525903222</v>
+        <v>-1.623373237172441</v>
       </c>
       <c r="E1865" t="n">
-        <v>2.617939317740096</v>
+        <v>2.460920233232408</v>
       </c>
       <c r="F1865" t="n">
         <v>0.4941466024518028</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108643</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-1.227668824873018</v>
+        <v>-1.620216536142237</v>
       </c>
       <c r="E1866" t="n">
-        <v>2.617196048761055</v>
+        <v>2.460176964253368</v>
       </c>
       <c r="F1866" t="n">
         <v>0.4941466024518028</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-1.231681857285539</v>
+        <v>-1.624229568554759</v>
       </c>
       <c r="E1867" t="n">
-        <v>2.625849526464726</v>
+        <v>2.468830441957038</v>
       </c>
       <c r="F1867" t="n">
         <v>0.4941466024518028</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-1.245396721610651</v>
+        <v>-1.63794443287987</v>
       </c>
       <c r="E1868" t="n">
-        <v>2.616463145880376</v>
+        <v>2.459444061372688</v>
       </c>
       <c r="F1868" t="n">
         <v>0.4941466024518028</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-1.250913641454617</v>
+        <v>-1.643461352723837</v>
       </c>
       <c r="E1869" t="n">
-        <v>2.612661297997791</v>
+        <v>2.455642213490103</v>
       </c>
       <c r="F1869" t="n">
         <v>0.4941466024518028</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-1.255726679919954</v>
+        <v>-1.648274391189174</v>
       </c>
       <c r="E1870" t="n">
-        <v>2.614515058540864</v>
+        <v>2.457495974033176</v>
       </c>
       <c r="F1870" t="n">
         <v>0.4925999677490169</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-1.253609521195661</v>
+        <v>-1.646157232464881</v>
       </c>
       <c r="E1871" t="n">
-        <v>2.611335617496178</v>
+        <v>2.45431653298849</v>
       </c>
       <c r="F1871" t="n">
         <v>0.4925999677490169</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-1.253132174617171</v>
+        <v>-1.645679885886391</v>
       </c>
       <c r="E1872" t="n">
-        <v>2.61142445480599</v>
+        <v>2.454405370298302</v>
       </c>
       <c r="F1872" t="n">
         <v>0.4925999677490169</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-1.252107388310314</v>
+        <v>-1.644655099579533</v>
       </c>
       <c r="E1873" t="n">
-        <v>2.614405885300163</v>
+        <v>2.457386800792476</v>
       </c>
       <c r="F1873" t="n">
         <v>0.4936247540558745</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-1.270848768569232</v>
+        <v>-1.663396479838452</v>
       </c>
       <c r="E1874" t="n">
-        <v>2.612259636494646</v>
+        <v>2.455240551986958</v>
       </c>
       <c r="F1874" t="n">
         <v>0.4936247540558745</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-1.283818111354331</v>
+        <v>-1.67636582262355</v>
       </c>
       <c r="E1875" t="n">
-        <v>2.614987919337784</v>
+        <v>2.457968834830096</v>
       </c>
       <c r="F1875" t="n">
         <v>0.4806554112707759</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-1.277341964560771</v>
+        <v>-1.669889675829991</v>
       </c>
       <c r="E1876" t="n">
-        <v>2.620620128676976</v>
+        <v>2.463601044169289</v>
       </c>
       <c r="F1876" t="n">
         <v>0.4871315580643355</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-1.27365103960436</v>
+        <v>-1.66619875087358</v>
       </c>
       <c r="E1877" t="n">
-        <v>2.622096498659541</v>
+        <v>2.465077414151853</v>
       </c>
       <c r="F1877" t="n">
         <v>0.4871315580643355</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-1.266435686732544</v>
+        <v>-1.658983398001764</v>
       </c>
       <c r="E1878" t="n">
-        <v>2.63049583692691</v>
+        <v>2.473476752419222</v>
       </c>
       <c r="F1878" t="n">
         <v>0.5569097933547174</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-1.215407840650718</v>
+        <v>-1.607955551919938</v>
       </c>
       <c r="E1879" t="n">
-        <v>2.655389529844076</v>
+        <v>2.498370445336389</v>
       </c>
       <c r="F1879" t="n">
         <v>0.6321191316618183</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-1.14193800898327</v>
+        <v>-1.534485720252489</v>
       </c>
       <c r="E1880" t="n">
-        <v>2.700149164004477</v>
+        <v>2.543130079496789</v>
       </c>
       <c r="F1880" t="n">
         <v>0.7055889633292667</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-1.06156565351934</v>
+        <v>-1.45411336478856</v>
       </c>
       <c r="E1881" t="n">
-        <v>2.746853326937566</v>
+        <v>2.589834242429878</v>
       </c>
       <c r="F1881" t="n">
         <v>0.7859613187931963</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-1.028633783706489</v>
+        <v>-1.421181494975709</v>
       </c>
       <c r="E1882" t="n">
-        <v>2.75280690996111</v>
+        <v>2.595787825453422</v>
       </c>
       <c r="F1882" t="n">
         <v>0.7859613187931963</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-1.048798425256037</v>
+        <v>-1.441346136525256</v>
       </c>
       <c r="E1883" t="n">
-        <v>2.738068862567315</v>
+        <v>2.581049778059627</v>
       </c>
       <c r="F1883" t="n">
         <v>0.765796677243649</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-0.9901314952345031</v>
+        <v>-1.382679206503723</v>
       </c>
       <c r="E1884" t="n">
-        <v>2.762651424414484</v>
+        <v>2.605632339906796</v>
       </c>
       <c r="F1884" t="n">
         <v>0.8507561456737867</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-0.9270622629281635</v>
+        <v>-1.319609974197383</v>
       </c>
       <c r="E1885" t="n">
-        <v>2.790572845966135</v>
+        <v>2.633553761458447</v>
       </c>
       <c r="F1885" t="n">
         <v>0.8222425829915522</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-0.8750467489593508</v>
+        <v>-1.26759446022857</v>
       </c>
       <c r="E1886" t="n">
-        <v>2.815369387240061</v>
+        <v>2.658350302732373</v>
       </c>
       <c r="F1886" t="n">
         <v>0.8222425829915522</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-0.6994770800384468</v>
+        <v>-1.092024791307666</v>
       </c>
       <c r="E1887" t="n">
-        <v>2.884122027909681</v>
+        <v>2.727102943401993</v>
       </c>
       <c r="F1887" t="n">
         <v>0.8222425829915522</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-0.5022076743104487</v>
+        <v>-0.894755385579668</v>
       </c>
       <c r="E1888" t="n">
-        <v>2.978083200365752</v>
+        <v>2.821064115858064</v>
       </c>
       <c r="F1888" t="n">
         <v>1.01951198871955</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-0.3030555670733495</v>
+        <v>-0.6956032783425689</v>
       </c>
       <c r="E1889" t="n">
-        <v>3.044692909613909</v>
+        <v>2.887673825106221</v>
       </c>
       <c r="F1889" t="n">
         <v>1.184834514669364</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-0.07721041435393849</v>
+        <v>-0.4697581256231579</v>
       </c>
       <c r="E1890" t="n">
-        <v>3.144610043737882</v>
+        <v>2.987590959230194</v>
       </c>
       <c r="F1890" t="n">
         <v>1.226761190256527</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>0.2090643979687559</v>
+        <v>-0.1834833133004635</v>
       </c>
       <c r="E1891" t="n">
-        <v>3.260259113223019</v>
+        <v>3.103240028715331</v>
       </c>
       <c r="F1891" t="n">
         <v>1.226761190256527</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>0.4358602250420898</v>
+        <v>0.04331251377287038</v>
       </c>
       <c r="E1892" t="n">
-        <v>3.35361121821446</v>
+        <v>3.196592133706772</v>
       </c>
       <c r="F1892" t="n">
         <v>1.294875134878072</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.371440683276648</v>
+        <v>3.391424541054112</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>0.7202336156982565</v>
+        <v>0.6803108856541815</v>
       </c>
       <c r="E1893" t="n">
-        <v>3.473094278715563</v>
+        <v>3.457125186697933</v>
       </c>
       <c r="F1893" t="n">
         <v>1.294875134878072</v>

--- a/tame_output/ON/bt/strategyON_20240305.xlsx
+++ b/tame_output/ON/bt/strategyON_20240305.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>299.7%</t>
+          <t>299.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006536</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.391424541054112</v>
+        <v>3.391424541054113</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>0.6803108856541815</v>
+        <v>0.6811608573467951</v>
       </c>
       <c r="E1893" t="n">
-        <v>3.457125186697933</v>
+        <v>3.457465175374979</v>
       </c>
       <c r="F1893" t="n">
         <v>1.294875134878072</v>

--- a/tame_output/ON/bt/strategyON_20240305.xlsx
+++ b/tame_output/ON/bt/strategyON_20240305.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>299.5%</t>
+          <t>388.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-93.5%</t>
+          <t>-128.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-44.6%</t>
         </is>
       </c>
     </row>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207816</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310985</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>0.6811608573467951</v>
+        <v>0.3272212447016193</v>
       </c>
       <c r="E1893" t="n">
-        <v>3.457465175374979</v>
+        <v>3.315889330316908</v>
       </c>
       <c r="F1893" t="n">
         <v>1.294875134878072</v>

--- a/tame_output/ON/bt/strategyON_20240305.xlsx
+++ b/tame_output/ON/bt/strategyON_20240305.xlsx
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207816</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310985</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
